--- a/tests/v1/fixtures/office6m/2026-09/bank_statements/HB_B_USD_2026-08.xlsx
+++ b/tests/v1/fixtures/office6m/2026-09/bank_statements/HB_B_USD_2026-08.xlsx
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>704314.35</v>
+        <v>706464.35</v>
       </c>
       <c r="E2" t="n">
         <v>75000.38</v>
       </c>
       <c r="F2" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
     </row>
     <row r="3">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
     </row>
     <row r="4">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
     </row>
     <row r="5">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
     </row>
     <row r="6">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
     </row>
     <row r="7">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
       <c r="E7" t="n">
         <v>200000</v>
       </c>
       <c r="F7" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="8">
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="9">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="10">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="11">
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="12">
@@ -979,13 +979,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="13">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="14">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="15">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="16">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="17">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
     </row>
     <row r="18">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>979314.73</v>
+        <v>981464.73</v>
       </c>
       <c r="E18" t="n">
         <v>-200000</v>
       </c>
       <c r="F18" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
     </row>
     <row r="19">
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
     </row>
     <row r="20">
@@ -1187,13 +1187,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
     </row>
     <row r="21">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>779314.73</v>
+        <v>781464.73</v>
       </c>
       <c r="E21" t="n">
         <v>-14765.11</v>
       </c>
       <c r="F21" t="n">
-        <v>764549.62</v>
+        <v>766699.62</v>
       </c>
     </row>
     <row r="22">
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>764549.62</v>
+        <v>766699.62</v>
       </c>
       <c r="E22" t="n">
         <v>273.35</v>
       </c>
       <c r="F22" t="n">
-        <v>764822.97</v>
+        <v>766972.97</v>
       </c>
     </row>
   </sheetData>
